--- a/product_upload/packages/66/file.xlsx
+++ b/product_upload/packages/66/file.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -645,6 +645,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -830,6 +835,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>BLOCAL 5 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-0611F6A85F36</t>
         </is>
       </c>
@@ -853,7 +863,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1022,6 +1032,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>ANAFRANIL TAB 10MG</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-41B2216AD636</t>
         </is>
       </c>
@@ -1045,7 +1060,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1218,6 +1233,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>ANAFRANIL TABLETS 25 MG</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-0225D675D5F2</t>
         </is>
       </c>
@@ -1241,7 +1261,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1412,6 +1432,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>VIBRAMYCIN 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-2A36A1001DE2</t>
         </is>
       </c>
@@ -1435,7 +1460,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1596,6 +1621,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>VALDATIN 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-58415BB5BF65</t>
         </is>
       </c>
@@ -1619,7 +1649,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1780,6 +1810,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>VALDATIN 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-3F1452A9E128</t>
         </is>
       </c>
@@ -1803,7 +1838,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1970,6 +2005,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>LEVETAM 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-21891A782684</t>
         </is>
       </c>
@@ -1993,7 +2033,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2162,6 +2202,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>MARLON 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-AC4522E46156</t>
         </is>
       </c>
@@ -2185,7 +2230,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2360,6 +2405,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>WELLBUTRIN XL 300 EXTENDED RELEASE F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-771708BF3F0D</t>
         </is>
       </c>
@@ -2383,7 +2433,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2550,6 +2600,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>NOYADA 25MG/5ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-AAE6FEBE56FE</t>
         </is>
       </c>
@@ -2573,7 +2628,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2740,6 +2795,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>NOYADA 5MG/5ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-7A4223E93D10</t>
         </is>
       </c>
@@ -2763,7 +2823,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2926,6 +2986,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>EZEACT PLUS 40MG/12.5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-505ECFB395B6</t>
         </is>
       </c>
@@ -2949,7 +3014,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3122,6 +3187,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>PENTASA XTEND 2 GM SACHET</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-EA2481736DD8</t>
         </is>
       </c>
@@ -3145,7 +3215,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3308,6 +3378,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>EZEACT PLUS 40MG/25MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-86BE5609891E</t>
         </is>
       </c>
@@ -3331,7 +3406,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3492,6 +3567,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>XOROLA 2.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-CC6CD2B76704</t>
         </is>
       </c>
@@ -3515,7 +3595,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3678,6 +3758,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>CANDEZA 8 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-04D5C4DB7582</t>
         </is>
       </c>
@@ -3701,7 +3786,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3864,6 +3949,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>CANDEZA 16 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-6B14A46ACEA5</t>
         </is>
       </c>
@@ -3887,7 +3977,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4052,6 +4142,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>CANDEZA 16/12.5 mg TABLETS</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-9378F12519B3</t>
         </is>
       </c>
@@ -4075,7 +4170,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4240,6 +4335,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>CANDEZA 8/12.5 mg TABLETS</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-144D077F374F</t>
         </is>
       </c>
@@ -4263,7 +4363,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4432,6 +4532,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>SNAFI 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-0A2292AC4B32</t>
         </is>
       </c>
@@ -4455,7 +4560,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4618,6 +4723,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>BRIVIACT 10MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-297940C65F3A</t>
         </is>
       </c>
@@ -4641,7 +4751,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4810,6 +4920,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>SILOMES 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-D9B6E5EF3B3B</t>
         </is>
       </c>
@@ -4833,7 +4948,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5002,6 +5117,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>SILOMES 100 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-E69C42E69D03</t>
         </is>
       </c>
@@ -5025,7 +5145,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5194,6 +5314,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>SILOMES 200 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-9C6BA49FB883</t>
         </is>
       </c>
@@ -5217,7 +5342,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5382,6 +5507,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>LIFANCE 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-2901658C27A6</t>
         </is>
       </c>
@@ -5405,7 +5535,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5570,6 +5700,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>LIFANCE 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-A8AC78F8B78B</t>
         </is>
       </c>
@@ -5593,7 +5728,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5764,6 +5899,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>LANOXIN 0.25MG TAB</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-5208C3A0C81A</t>
         </is>
       </c>
@@ -5787,7 +5927,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5960,6 +6100,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>TYRA 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-A3783FA4D80A</t>
         </is>
       </c>
@@ -5983,7 +6128,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6150,6 +6295,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>CLERON 250MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-37433B38949D</t>
         </is>
       </c>
@@ -6173,7 +6323,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6336,6 +6486,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>RESEDRA 1MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-92F1AB57C14F</t>
         </is>
       </c>
@@ -6359,7 +6514,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6522,6 +6677,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>CLERON 500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-8DC612E99B04</t>
         </is>
       </c>
@@ -6545,7 +6705,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6706,6 +6866,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>KLENDAM</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-BD8E9FC66969</t>
         </is>
       </c>
@@ -6729,7 +6894,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6892,6 +7057,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>AMLOVAN-HCT 10/320/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-0275E0E4C09A</t>
         </is>
       </c>
@@ -6915,7 +7085,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7074,6 +7244,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>KINZADO</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-52BEE65A9045</t>
         </is>
       </c>
@@ -7097,7 +7272,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7262,6 +7437,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>MIXIF</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-0F5307FD1033</t>
         </is>
       </c>
@@ -7285,7 +7465,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7454,6 +7634,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>CROTAL 1MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-13BCC11F985B</t>
         </is>
       </c>
@@ -7477,7 +7662,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7646,6 +7831,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>CROTAL 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-1F0939CF4F56</t>
         </is>
       </c>
@@ -7669,7 +7859,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7832,6 +8022,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>Altan</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-EA49699A77FF</t>
         </is>
       </c>
@@ -7855,7 +8050,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8018,6 +8213,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Batlor</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-C0DE831DF3C0</t>
         </is>
       </c>
@@ -8041,7 +8241,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8204,6 +8404,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>Barolex</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-759CDC45E8A0</t>
         </is>
       </c>
@@ -8227,7 +8432,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8386,6 +8591,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>Barolex</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-F19649652EDE</t>
         </is>
       </c>
@@ -8409,7 +8619,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8576,6 +8786,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>Catafenac</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-9A72B5FD79A8</t>
         </is>
       </c>
@@ -8599,7 +8814,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8758,6 +8973,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>Catafenac</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-CFADCEAA963D</t>
         </is>
       </c>
@@ -8781,7 +9001,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8944,6 +9164,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>Esoxo</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-F7C29C3B47BC</t>
         </is>
       </c>
@@ -8967,7 +9192,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9130,6 +9355,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Esoxo</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-FDE0C72400BB</t>
         </is>
       </c>
@@ -9153,7 +9383,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9322,6 +9552,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>Provecta</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-FB439F5BD498</t>
         </is>
       </c>
@@ -9345,7 +9580,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9510,6 +9745,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>Lijen</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-B790335334B2</t>
         </is>
       </c>
@@ -9533,7 +9773,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9702,6 +9942,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>OLYMA</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-637631819FF1</t>
         </is>
       </c>
@@ -9725,7 +9970,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9888,6 +10133,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>Forsdapa</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-5347FD886F4D</t>
         </is>
       </c>
@@ -9911,7 +10161,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10078,6 +10328,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>Leracet</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-B1F931FA8BE0</t>
         </is>
       </c>
@@ -10101,7 +10356,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10264,6 +10519,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>Leracet</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-E1CB2CBDF251</t>
         </is>
       </c>
@@ -10287,7 +10547,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10454,6 +10714,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>EMBA</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-C65CC877D3FE</t>
         </is>
       </c>
@@ -10477,7 +10742,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10640,6 +10905,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>EMBA</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-7F407137B288</t>
         </is>
       </c>
@@ -10663,7 +10933,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10830,6 +11100,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>clopidogrel ALH</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-B0DDF7A42D7C</t>
         </is>
       </c>
@@ -10853,7 +11128,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11016,6 +11291,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>Sitagia</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-B36DE3F0D354</t>
         </is>
       </c>
@@ -11039,7 +11319,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11198,6 +11478,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>Zolabri</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-C3E8978DE19D</t>
         </is>
       </c>
@@ -11221,7 +11506,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11384,6 +11669,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>Zolabri</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-586D2485AD46</t>
         </is>
       </c>
@@ -11407,7 +11697,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11574,6 +11864,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>Zolabri</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-5FA925C0A894</t>
         </is>
       </c>
@@ -11597,7 +11892,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11760,6 +12055,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>Zolabri</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-82C84FC10ACB</t>
         </is>
       </c>
@@ -11783,7 +12083,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11950,6 +12250,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>Zolabri</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-F5C1AE71A11E</t>
         </is>
       </c>
@@ -11973,7 +12278,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12136,6 +12441,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>Jedara</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-72A0D4024FB9</t>
         </is>
       </c>
@@ -12159,7 +12469,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12322,6 +12632,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>TIDILOR</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-EBCBFC11B864</t>
         </is>
       </c>
@@ -12345,7 +12660,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12518,6 +12833,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>Helt</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-777C4B0C94DE</t>
         </is>
       </c>
@@ -12541,7 +12861,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12704,6 +13024,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>Glofel</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-4D244698BB07</t>
         </is>
       </c>
@@ -12727,7 +13052,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12886,6 +13211,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>Olmidip HCT</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-FB86F81E7C6C</t>
         </is>
       </c>
@@ -12909,7 +13239,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13072,6 +13402,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>Olmidip HCT</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-0957C184EEE6</t>
         </is>
       </c>
@@ -13095,7 +13430,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13258,6 +13593,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>Olmidip HCT</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-FC569621BB20</t>
         </is>
       </c>
@@ -13281,7 +13621,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13440,6 +13780,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>Olmidip HCT</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-C75309FE1E19</t>
         </is>
       </c>
@@ -13463,7 +13808,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13626,6 +13971,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>Olmidip HCT</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-14F7B2EE4710</t>
         </is>
       </c>
@@ -13649,7 +13999,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13812,6 +14162,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>Solitrol</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-62DBE9A0E2B1</t>
         </is>
       </c>
@@ -13835,7 +14190,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14002,6 +14357,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>Solitrol</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-BB4C8F294B3D</t>
         </is>
       </c>
@@ -14025,7 +14385,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14192,6 +14552,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>Coduro</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-66E2C5E3833E</t>
         </is>
       </c>
@@ -14215,7 +14580,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14374,6 +14739,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>Coduro</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-A1128CE7F833</t>
         </is>
       </c>
@@ -14397,7 +14767,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14564,6 +14934,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>Coduro</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-C022C9005199</t>
         </is>
       </c>
@@ -14587,7 +14962,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14750,6 +15125,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>EZIUM</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-1980F9E83A20</t>
         </is>
       </c>
@@ -14773,7 +15153,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14936,6 +15316,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>EZIUM</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-AE28A34E2537</t>
         </is>
       </c>
@@ -14959,7 +15344,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15118,6 +15503,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>EZIUM</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-734E8D0F0BA1</t>
         </is>
       </c>
@@ -15141,7 +15531,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15304,6 +15694,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>EZIUM</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-6739785906BE</t>
         </is>
       </c>
@@ -15327,7 +15722,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15490,6 +15885,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>Dapagloz</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-EA1D444C8504</t>
         </is>
       </c>
@@ -15513,7 +15913,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15680,6 +16080,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>Dapagloz</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-EA09531CD2DB</t>
         </is>
       </c>
@@ -15703,7 +16108,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15872,6 +16277,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>Pulmistad</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-D591C71B63E0</t>
         </is>
       </c>
@@ -15895,7 +16305,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16064,6 +16474,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>Pulmistad</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-534580DA8B64</t>
         </is>
       </c>
@@ -16087,7 +16502,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16254,6 +16669,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>Telfast</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-BF635B3C128E</t>
         </is>
       </c>
@@ -16277,7 +16697,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16452,6 +16872,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>Telfast</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-D149665CBC5D</t>
         </is>
       </c>
@@ -16475,7 +16900,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16638,6 +17063,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>Celavas</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-555530AAA130</t>
         </is>
       </c>
@@ -16661,7 +17091,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16824,6 +17254,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>SITAJUB</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-B6E6F2517933</t>
         </is>
       </c>
@@ -16847,7 +17282,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17014,6 +17449,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>Glynta</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-6F48A73E07B6</t>
         </is>
       </c>
@@ -17037,7 +17477,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17204,6 +17644,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Restorica - D3</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-3C7FB914547C</t>
         </is>
       </c>
@@ -17227,7 +17672,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17394,6 +17839,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Losapil</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-A3B69F19E133</t>
         </is>
       </c>
@@ -17417,7 +17867,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17576,6 +18026,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>Losapil</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-9244C348A62C</t>
         </is>
       </c>
@@ -17599,7 +18054,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17762,6 +18217,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>Losapil</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-8261F6548674</t>
         </is>
       </c>
@@ -17785,7 +18245,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17952,6 +18412,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>Altan</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-087366C253AE</t>
         </is>
       </c>
@@ -17975,7 +18440,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18142,6 +18607,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>Survilor</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-F5ECD55FBF2C</t>
         </is>
       </c>
@@ -18165,7 +18635,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18332,6 +18802,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>chinasi</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-39F20A4A9008</t>
         </is>
       </c>
@@ -18355,7 +18830,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18518,6 +18993,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>Chinasi</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-F071955BE41A</t>
         </is>
       </c>
@@ -18541,7 +19021,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18704,6 +19184,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>Chinasi</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-0CDE98BD19EF</t>
         </is>
       </c>
@@ -18727,7 +19212,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18894,6 +19379,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Dapagliflozin Evapharma</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-298BCBEBD01B</t>
         </is>
       </c>
@@ -18917,7 +19407,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19080,6 +19570,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Dapagliflozin Evapharma</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-FCACF11C2A6E</t>
         </is>
       </c>
@@ -19103,7 +19598,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19266,6 +19761,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>Letno</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-83B1A8245500</t>
         </is>
       </c>
@@ -19289,7 +19789,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19447,6 +19947,11 @@
       <c r="AR101" t="inlineStr"/>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Vtreat Met</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-B453355BC885</t>
         </is>
@@ -19463,7 +19968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19509,100 +20014,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19634,7 +20144,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19649,92 +20159,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-46940</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>128.29</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>674</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19766,7 +20281,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19781,92 +20296,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-76308</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>219.37</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>675</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19898,7 +20418,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19913,92 +20433,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-74754</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>104.57</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>676</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20030,7 +20555,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20045,92 +20570,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-91868</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>442.01</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>677</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20162,7 +20692,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20177,92 +20707,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-34863</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>356</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>678</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20294,7 +20829,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20309,92 +20844,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-54526</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>34.13</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>679</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20426,7 +20966,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20441,92 +20981,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-41854</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>164.94</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>680</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20558,7 +21103,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20573,92 +21118,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-96388</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>124.85</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>681</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20690,7 +21240,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20705,92 +21255,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-78041</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>197.27</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>682</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20822,7 +21377,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20837,92 +21392,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-37177</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>242.49</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>683</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20954,7 +21514,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20969,92 +21529,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-43688</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>107.75</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>684</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21071,7 +21636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21177,6 +21742,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21212,7 +21787,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21277,6 +21852,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-E526C7F832D4</t>
         </is>
@@ -21313,7 +21898,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21378,6 +21963,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-99799CEC78D5</t>
         </is>
@@ -21414,7 +22009,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21479,6 +22074,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-8615DC645C3E</t>
         </is>
@@ -21515,7 +22120,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21580,6 +22185,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-0C7513F17CB7</t>
         </is>
@@ -21616,7 +22231,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21681,6 +22296,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-F37E131F86E7</t>
         </is>
@@ -21717,7 +22342,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21782,6 +22407,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-FD9659F27D7E</t>
         </is>
@@ -21818,7 +22453,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21883,6 +22518,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-01A5C3EE0112</t>
         </is>
@@ -21919,7 +22564,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21984,6 +22629,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-E6982F1DB933</t>
         </is>
@@ -22020,7 +22675,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22085,6 +22740,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-D4F126793DDB</t>
         </is>
@@ -22121,7 +22786,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22186,6 +22851,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-69E0A162515C</t>
         </is>
@@ -22222,7 +22897,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22287,6 +22962,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-A17FD4F3B49C</t>
         </is>
@@ -22323,7 +23008,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22388,6 +23073,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-960BC83339C5</t>
         </is>
@@ -22424,7 +23119,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22489,6 +23184,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-620587DA434F</t>
         </is>
@@ -22525,7 +23230,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22590,6 +23295,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-CC8D367E84F7</t>
         </is>
@@ -22626,7 +23341,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22691,6 +23406,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-8409163D1674</t>
         </is>
@@ -22727,7 +23452,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22792,6 +23517,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-95F64A5E00E4</t>
         </is>
@@ -22828,7 +23563,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22893,6 +23628,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-BC9AA0ED7BC3</t>
         </is>
@@ -22929,7 +23674,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22994,6 +23739,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-34B2D344A3C9</t>
         </is>
@@ -23030,7 +23785,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23095,6 +23850,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-162CFA93A06E</t>
         </is>
@@ -23131,7 +23896,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23196,6 +23961,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-B8882F9276E1</t>
         </is>

--- a/product_upload/packages/66/file.xlsx
+++ b/product_upload/packages/66/file.xlsx
@@ -682,8 +682,16 @@
           <t>4188754424-184-341967573468</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BLOCAL 5 mg capsule</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>BLOCAL 5 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -1468,8 +1476,16 @@
           <t>9136196516-027-926446077724</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VALDATIN 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>VALDATIN 50MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1657,8 +1673,16 @@
           <t>1359924703-236-568700114325</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VALDATIN 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VALDATIN 50MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1846,8 +1870,16 @@
           <t>3698664426-688-043800664503</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVETAM 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>LEVETAM 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -2441,8 +2473,16 @@
           <t>8382430584-511-273550591506</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOYADA 25MG/5ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NOYADA 25MG/5ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2636,8 +2676,16 @@
           <t>2920817445-115-307100070064</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOYADA 5MG/5ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NOYADA 5MG/5ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2831,8 +2879,16 @@
           <t>8141321705-682-391285534538</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZEACT PLUS 40MG/12.5MG TABLET</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>EZEACT PLUS 40MG/12.5MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3223,8 +3279,16 @@
           <t>9195137891-058-399472447583</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZEACT PLUS 40MG/25MG TABLET</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>EZEACT PLUS 40MG/25MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3414,8 +3478,16 @@
           <t>5601075651-299-548023468065</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XOROLA 2.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>XOROLA 2.5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3603,8 +3675,16 @@
           <t>7740243786-713-957874120542</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDEZA 8 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CANDEZA 8 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -3794,8 +3874,16 @@
           <t>1239897482-491-070262959856</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDEZA 16 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CANDEZA 16 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -3985,8 +4073,16 @@
           <t>0380324546-182-803516025695</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDEZA 16/12.5 mg TABLETS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CANDEZA 16/12.5 mg TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -4178,8 +4274,16 @@
           <t>3035041642-012-825012112355</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDEZA 8/12.5 mg TABLETS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CANDEZA 8/12.5 mg TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -4568,8 +4672,16 @@
           <t>9928637344-651-123352591284</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRIVIACT 10MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>BRIVIACT 10MG/ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -5350,8 +5462,16 @@
           <t>4831744224-141-864054064778</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIFANCE 5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>LIFANCE 5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5543,8 +5663,16 @@
           <t>8414145947-457-129786978715</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIFANCE 10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>LIFANCE 10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -6136,8 +6264,16 @@
           <t>4535005863-194-017785529701</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLERON 250MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CLERON 250MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6331,8 +6467,16 @@
           <t>1167713907-132-577623838324</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESEDRA 1MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>RESEDRA 1MG/ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6522,8 +6666,16 @@
           <t>3086438686-210-227740198067</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLERON 500MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CLERON 500MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6713,8 +6865,16 @@
           <t>0260921928-860-947599220458</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KLENDAM</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>KLENDAM detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6902,8 +7062,16 @@
           <t>1580959779-986-685043734451</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOVAN-HCT 10/320/25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>AMLOVAN-HCT 10/320/25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7093,8 +7261,16 @@
           <t>8916508672-503-697118842264</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KINZADO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>KINZADO detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7280,8 +7456,16 @@
           <t>3840096596-625-962776673458</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MIXIF</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>MIXIF detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7867,8 +8051,16 @@
           <t>8677217882-852-729633467418</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Altan</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Altan detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8058,8 +8250,16 @@
           <t>0280411117-256-022546273486</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Batlor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Batlor detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8249,8 +8449,16 @@
           <t>1407633489-542-513358561723</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Barolex</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Barolex detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8440,8 +8648,16 @@
           <t>7865220393-065-051552400034</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Barolex</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Barolex detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8627,8 +8843,16 @@
           <t>3999016439-329-101386745957</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Catafenac</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Catafenac detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8822,8 +9046,16 @@
           <t>4266406620-019-167435816638</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Catafenac</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Catafenac detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9009,8 +9241,16 @@
           <t>1070478923-595-004364375147</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Esoxo</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Esoxo detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9200,8 +9440,16 @@
           <t>2115518641-735-585757306971</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Esoxo</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Esoxo detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9391,8 +9639,16 @@
           <t>3815444305-223-651773618074</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Provecta</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Provecta detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9588,8 +9844,16 @@
           <t>3016239066-316-637479959292</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lijen</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Lijen detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9781,8 +10045,16 @@
           <t>2396397466-067-323489473488</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLYMA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>OLYMA detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9978,8 +10250,16 @@
           <t>0635806964-474-244793373991</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Forsdapa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Forsdapa detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10169,8 +10449,16 @@
           <t>4313695912-011-823850307770</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Leracet</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Leracet detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10364,8 +10652,16 @@
           <t>3856921331-680-833102871587</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Leracet</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Leracet detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10555,8 +10851,16 @@
           <t>8456217170-972-308158558376</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMBA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>EMBA detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10750,8 +11054,16 @@
           <t>7244579155-424-695382929119</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMBA</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>EMBA detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10941,8 +11253,16 @@
           <t>1891605648-833-238180683508</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ clopidogrel ALH</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>clopidogrel ALH detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11136,8 +11456,16 @@
           <t>4642949672-745-687147106990</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sitagia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sitagia detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11327,8 +11655,16 @@
           <t>5403378907-686-268762312244</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zolabri</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Zolabri detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11514,8 +11850,16 @@
           <t>7797536562-005-502871509456</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zolabri</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Zolabri detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11705,8 +12049,16 @@
           <t>1575454262-098-473289757497</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zolabri</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Zolabri detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11900,8 +12252,16 @@
           <t>3410710270-076-816720102236</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zolabri</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Zolabri detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12091,8 +12451,16 @@
           <t>6445589866-485-540315013752</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zolabri</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Zolabri detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12286,8 +12654,16 @@
           <t>9319016924-270-198287946936</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Jedara</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Jedara detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12477,8 +12853,16 @@
           <t>0968100822-104-138197405496</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TIDILOR</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>TIDILOR detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12869,8 +13253,16 @@
           <t>8158713678-499-093689163924</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Glofel</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Glofel detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13060,8 +13452,16 @@
           <t>1448932055-093-444061671597</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmidip HCT</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Olmidip HCT detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13247,8 +13647,16 @@
           <t>2963856284-213-781086908653</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmidip HCT</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Olmidip HCT detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13438,8 +13846,16 @@
           <t>7205947621-780-587738684274</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmidip HCT</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Olmidip HCT detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13629,8 +14045,16 @@
           <t>7576869895-038-482239562819</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmidip HCT</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Olmidip HCT detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13816,8 +14240,16 @@
           <t>5103042915-727-014969507309</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olmidip HCT</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Olmidip HCT detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14007,8 +14439,16 @@
           <t>2141099987-569-186696492157</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Solitrol</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Solitrol detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14198,8 +14638,16 @@
           <t>3844817597-384-150732074305</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Solitrol</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Solitrol detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14393,8 +14841,16 @@
           <t>0345632114-933-618941187352</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coduro</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Coduro detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14588,8 +15044,16 @@
           <t>3839788664-349-263660680518</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coduro</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Coduro detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14775,8 +15239,16 @@
           <t>4332892011-486-119156278379</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coduro</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Coduro detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14970,8 +15442,16 @@
           <t>5545627633-451-212282995971</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZIUM</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>EZIUM detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15161,8 +15641,16 @@
           <t>2702923979-398-814923959745</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZIUM</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>EZIUM detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15352,8 +15840,16 @@
           <t>1940852159-405-887013110617</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZIUM</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>EZIUM detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15539,8 +16035,16 @@
           <t>8313190525-842-714786685252</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZIUM</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>EZIUM detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15730,8 +16234,16 @@
           <t>4447790467-130-928461329962</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dapagloz</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Dapagloz detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15921,8 +16433,16 @@
           <t>1763815748-014-311826735873</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dapagloz</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Dapagloz detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16116,8 +16636,16 @@
           <t>1267326803-404-354874424620</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pulmistad</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Pulmistad detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16313,8 +16841,16 @@
           <t>3863225706-287-588376458887</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pulmistad</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Pulmistad detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16510,8 +17046,16 @@
           <t>3890594001-851-915911080178</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Telfast</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Telfast detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16908,8 +17452,16 @@
           <t>5723858213-561-732844729605</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Celavas</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Celavas detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17099,8 +17651,16 @@
           <t>4003298732-649-793951999970</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SITAJUB</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>SITAJUB detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17290,8 +17850,16 @@
           <t>1951999557-641-146827934012</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Glynta</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Glynta detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17485,8 +18053,16 @@
           <t>9426896808-039-788091230115</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Restorica - D3</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Restorica - D3 detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17680,8 +18256,16 @@
           <t>6697510027-971-765936126728</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Losapil</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Losapil detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17875,8 +18459,16 @@
           <t>0030674169-594-742837873237</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Losapil</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Losapil detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18062,8 +18654,16 @@
           <t>4297421620-260-542241091269</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Losapil</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Losapil detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18253,8 +18853,16 @@
           <t>2296049749-462-089027727135</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Altan</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Altan detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18448,8 +19056,16 @@
           <t>1110458976-526-942827667821</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Survilor</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Survilor detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18643,8 +19259,16 @@
           <t>1818067844-897-168056044811</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ chinasi</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>chinasi detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18838,8 +19462,16 @@
           <t>7945930147-866-514569505020</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Chinasi</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Chinasi detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19029,8 +19661,16 @@
           <t>2311833622-769-400803929891</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Chinasi</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Chinasi detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19220,8 +19860,16 @@
           <t>5112702601-695-513431963087</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dapagliflozin Evapharma</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Dapagliflozin Evapharma detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19415,8 +20063,16 @@
           <t>0879180839-539-534570920143</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dapagliflozin Evapharma</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Dapagliflozin Evapharma detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19606,8 +20262,16 @@
           <t>3953096751-993-539681498496</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Letno</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Letno detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19797,8 +20461,16 @@
           <t>4013970866-791-354832624839</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vtreat Met</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Vtreat Met detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/66/file.xlsx
+++ b/product_upload/packages/66/file.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -759,8 +759,10 @@
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0</v>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -956,8 +958,10 @@
       <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="n">
-        <v>0</v>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -1153,8 +1157,10 @@
       <c r="Y4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0</v>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -1354,8 +1360,10 @@
       <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="n">
-        <v>0</v>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1553,8 +1561,10 @@
       <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" t="n">
-        <v>0</v>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1750,8 +1760,10 @@
       <c r="Y7" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0</v>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1949,8 +1961,10 @@
       <c r="Y8" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0</v>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -2150,8 +2164,10 @@
       <c r="Y9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" t="n">
-        <v>0</v>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -2349,8 +2365,10 @@
       <c r="Y10" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0</v>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -2958,8 +2976,10 @@
       <c r="Y13" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" t="n">
-        <v>0</v>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -3155,8 +3175,10 @@
       <c r="Y14" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" t="n">
-        <v>0</v>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -3358,8 +3380,10 @@
       <c r="Y15" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0</v>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -3555,8 +3579,10 @@
       <c r="Y16" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" t="n">
-        <v>0</v>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -3754,8 +3780,10 @@
       <c r="Y17" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" t="n">
-        <v>0</v>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -3953,8 +3981,10 @@
       <c r="Y18" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" t="n">
-        <v>0</v>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -4154,8 +4184,10 @@
       <c r="Y19" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" t="n">
-        <v>0</v>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -4355,8 +4387,10 @@
       <c r="Y20" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" t="n">
-        <v>0</v>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -4552,8 +4586,10 @@
       <c r="Y21" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" t="n">
-        <v>0</v>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -4948,8 +4984,10 @@
       <c r="Y23" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" t="n">
-        <v>0</v>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -5145,8 +5183,10 @@
       <c r="Y24" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" t="n">
-        <v>0</v>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -5342,8 +5382,10 @@
       <c r="Y25" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" t="n">
-        <v>0</v>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -5539,8 +5581,10 @@
       <c r="Y26" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" t="n">
-        <v>0</v>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -5740,8 +5784,10 @@
       <c r="Y27" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" t="n">
-        <v>0</v>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -5941,8 +5987,10 @@
       <c r="Y28" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" t="n">
-        <v>0</v>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -6140,8 +6188,10 @@
       <c r="Y29" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" t="n">
-        <v>0</v>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
@@ -6341,8 +6391,10 @@
       <c r="Y30" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" t="n">
-        <v>0</v>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -6743,8 +6795,10 @@
       <c r="Y32" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" t="n">
-        <v>0</v>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -6942,8 +6996,10 @@
       <c r="Y33" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" t="n">
-        <v>0</v>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -7141,8 +7197,10 @@
       <c r="Y34" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" t="n">
-        <v>0</v>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -7340,8 +7398,10 @@
       <c r="Y35" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" t="n">
-        <v>0</v>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
@@ -7734,8 +7794,10 @@
       <c r="Y37" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" t="n">
-        <v>0</v>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
@@ -7931,8 +7993,10 @@
       <c r="Y38" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" t="n">
-        <v>0</v>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -8130,8 +8194,10 @@
       <c r="Y39" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" t="n">
-        <v>0</v>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -8329,8 +8395,10 @@
       <c r="Y40" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" t="n">
-        <v>0</v>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -8528,8 +8596,10 @@
       <c r="Y41" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" t="n">
-        <v>0</v>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -8727,8 +8797,10 @@
       <c r="Y42" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" t="n">
-        <v>0</v>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -8922,8 +8994,10 @@
       <c r="Y43" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" t="n">
-        <v>0</v>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -9125,8 +9199,10 @@
       <c r="Y44" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" t="n">
-        <v>0</v>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -9320,8 +9396,10 @@
       <c r="Y45" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" t="n">
-        <v>0</v>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
@@ -9519,8 +9597,10 @@
       <c r="Y46" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" t="n">
-        <v>0</v>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
@@ -9923,8 +10003,10 @@
       <c r="Y48" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" t="n">
-        <v>0</v>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -10124,8 +10206,10 @@
       <c r="Y49" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" t="n">
-        <v>0</v>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -10329,8 +10413,10 @@
       <c r="Y50" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" t="n">
-        <v>0</v>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -10528,8 +10614,10 @@
       <c r="Y51" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" t="n">
-        <v>0</v>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -10731,8 +10819,10 @@
       <c r="Y52" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" t="n">
-        <v>0</v>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -10930,8 +11020,10 @@
       <c r="Y53" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" t="n">
-        <v>0</v>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -11133,8 +11225,10 @@
       <c r="Y54" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" t="n">
-        <v>0</v>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -11332,8 +11426,10 @@
       <c r="Y55" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" t="n">
-        <v>0</v>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -11535,8 +11631,10 @@
       <c r="Y56" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" t="n">
-        <v>0</v>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -11734,8 +11832,10 @@
       <c r="Y57" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" t="n">
-        <v>0</v>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -11929,8 +12029,10 @@
       <c r="Y58" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" t="n">
-        <v>0</v>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -12128,8 +12230,10 @@
       <c r="Y59" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" t="n">
-        <v>0</v>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
@@ -12331,8 +12435,10 @@
       <c r="Y60" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" t="n">
-        <v>0</v>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
@@ -12530,8 +12636,10 @@
       <c r="Y61" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" t="n">
-        <v>0</v>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -12733,8 +12841,10 @@
       <c r="Y62" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" t="n">
-        <v>0</v>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -12932,8 +13042,10 @@
       <c r="Y63" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" t="n">
-        <v>0</v>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -13131,8 +13243,10 @@
       <c r="Y64" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" t="n">
-        <v>0</v>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -13332,8 +13446,10 @@
       <c r="Y65" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" t="n">
-        <v>0</v>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -13531,8 +13647,10 @@
       <c r="Y66" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" t="n">
-        <v>0</v>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
@@ -13726,8 +13844,10 @@
       <c r="Y67" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" t="n">
-        <v>0</v>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
@@ -13925,8 +14045,10 @@
       <c r="Y68" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" t="n">
-        <v>0</v>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
@@ -14124,8 +14246,10 @@
       <c r="Y69" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" t="n">
-        <v>0</v>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -14319,8 +14443,10 @@
       <c r="Y70" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" t="n">
-        <v>0</v>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
@@ -14518,8 +14644,10 @@
       <c r="Y71" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" t="n">
-        <v>0</v>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -14717,8 +14845,10 @@
       <c r="Y72" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" t="n">
-        <v>0</v>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
@@ -14920,8 +15050,10 @@
       <c r="Y73" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" t="n">
-        <v>0</v>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -15123,8 +15255,10 @@
       <c r="Y74" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" t="n">
-        <v>0</v>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -15318,8 +15452,10 @@
       <c r="Y75" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" t="n">
-        <v>0</v>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -15521,8 +15657,10 @@
       <c r="Y76" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" t="n">
-        <v>0</v>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
@@ -15720,8 +15858,10 @@
       <c r="Y77" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" t="n">
-        <v>0</v>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
@@ -15919,8 +16059,10 @@
       <c r="Y78" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" t="n">
-        <v>0</v>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -16114,8 +16256,10 @@
       <c r="Y79" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" t="n">
-        <v>0</v>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
@@ -16313,8 +16457,10 @@
       <c r="Y80" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" t="n">
-        <v>0</v>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
@@ -16512,8 +16658,10 @@
       <c r="Y81" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" t="n">
-        <v>0</v>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
@@ -17125,8 +17273,10 @@
       <c r="Y84" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" t="n">
-        <v>0</v>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
@@ -17328,8 +17478,10 @@
       <c r="Y85" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" t="n">
-        <v>0</v>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
@@ -17531,8 +17683,10 @@
       <c r="Y86" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" t="n">
-        <v>0</v>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
@@ -17730,8 +17884,10 @@
       <c r="Y87" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" t="n">
-        <v>0</v>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
@@ -17929,8 +18085,10 @@
       <c r="Y88" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" t="n">
-        <v>0</v>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
@@ -18132,8 +18290,10 @@
       <c r="Y89" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" t="n">
-        <v>0</v>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>iu</t>
+        </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
@@ -18335,8 +18495,10 @@
       <c r="Y90" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" t="n">
-        <v>0</v>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
@@ -18538,8 +18700,10 @@
       <c r="Y91" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" t="n">
-        <v>0</v>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
@@ -18733,8 +18897,10 @@
       <c r="Y92" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" t="n">
-        <v>0</v>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
@@ -18932,8 +19098,10 @@
       <c r="Y93" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" t="n">
-        <v>0</v>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
@@ -19135,8 +19303,10 @@
       <c r="Y94" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" t="n">
-        <v>0</v>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
@@ -19338,8 +19508,10 @@
       <c r="Y95" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" t="n">
-        <v>0</v>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
@@ -19541,8 +19713,10 @@
       <c r="Y96" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" t="n">
-        <v>0</v>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
@@ -19740,8 +19914,10 @@
       <c r="Y97" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" t="n">
-        <v>0</v>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
@@ -19939,8 +20115,10 @@
       <c r="Y98" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" t="n">
-        <v>0</v>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
@@ -20142,8 +20320,10 @@
       <c r="Y99" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" t="n">
-        <v>0</v>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
@@ -20341,8 +20521,10 @@
       <c r="Y100" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" t="n">
-        <v>0</v>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
@@ -20540,8 +20722,10 @@
       <c r="Y101" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" t="n">
-        <v>0</v>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
@@ -20686,7 +20870,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22308,7 +22492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22389,40 +22573,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22502,38 +22691,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>449.14</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-E526C7F832D4</t>
         </is>
@@ -22613,38 +22807,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>204.27</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-99799CEC78D5</t>
         </is>
@@ -22724,38 +22923,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>260.27</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-8615DC645C3E</t>
         </is>
@@ -22835,38 +23039,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>156.2</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-0C7513F17CB7</t>
         </is>
@@ -22946,38 +23155,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>369.2</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-F37E131F86E7</t>
         </is>
@@ -23057,38 +23271,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>109.63</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-FD9659F27D7E</t>
         </is>
@@ -23168,38 +23387,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>31.41</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-01A5C3EE0112</t>
         </is>
@@ -23279,38 +23503,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>352.48</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-E6982F1DB933</t>
         </is>
@@ -23390,38 +23619,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>214.06</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-D4F126793DDB</t>
         </is>
@@ -23501,38 +23735,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>122.89</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-69E0A162515C</t>
         </is>
@@ -23612,38 +23851,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>300.5</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-A17FD4F3B49C</t>
         </is>
@@ -23723,38 +23967,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>108.27</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-960BC83339C5</t>
         </is>
@@ -23834,38 +24083,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>145.98</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-620587DA434F</t>
         </is>
@@ -23945,38 +24199,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>485.45</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-CC8D367E84F7</t>
         </is>
@@ -24056,38 +24315,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>477.24</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-8409163D1674</t>
         </is>
@@ -24167,38 +24431,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>163.65</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-95F64A5E00E4</t>
         </is>
@@ -24278,38 +24547,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>232.92</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-BC9AA0ED7BC3</t>
         </is>
@@ -24389,38 +24663,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>274.69</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-34B2D344A3C9</t>
         </is>
@@ -24500,38 +24779,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>35.32</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-162CFA93A06E</t>
         </is>
@@ -24611,38 +24895,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>11</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-B8882F9276E1</t>
         </is>
